--- a/Email-Master/07 Test-Btach.xlsx
+++ b/Email-Master/07 Test-Btach.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Main data\Desktop\Log\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kapl\Desktop\Project-Reporting-Automation\Email-Master\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B11FF4-443F-4BE0-AF54-4ABE5BE57FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8595"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">List!$A$1:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">List!$A$1:$F$1</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>Receiver</t>
   </si>
@@ -41,34 +42,44 @@
     <t>Subject</t>
   </si>
   <si>
-    <t>Gourav Kothari &lt;gourav@kotharigroupindia.com&gt;</t>
-  </si>
-  <si>
-    <t>\\192.168.1.237\Accounts\SURESH_KAKEE_AUTOMATION PROJECTS\MANAGEMENT\07. Kothari Gaurav Ujwal\Report - 2025-26\MIS REPORT_Mr. Gourav Kothari Sir -2025-26.xlsb</t>
-  </si>
-  <si>
     <t>Attachement Path</t>
   </si>
   <si>
     <t>Schedule Time</t>
   </si>
   <si>
-    <t>After 11.00 PM Data Update Completion</t>
-  </si>
-  <si>
-    <t>New_MIS Report - 2025-26</t>
+    <t>IT&lt;it@kotharigroupindia.com&gt;</t>
+  </si>
+  <si>
+    <t>NEW_RM Debtors Outstanding Report</t>
+  </si>
+  <si>
+    <t>\\192.168.1.237\Accounts\SURESH_KAKEE_AUTOMATION PROJECTS\001 Auto Reports\006 ALL 11.00 AM Reports\RM Debtors Outstanding Report_New-2026-27.xlsb</t>
+  </si>
+  <si>
+    <t>After 11.00 AM Data Update Completion</t>
+  </si>
+  <si>
+    <t>\\192.168.1.237\Accounts\SURESH_KAKEE_AUTOMATION PROJECTS\SOLAPUR (HO)\00. Costing Reports\Stock Ageing Report.xlsb</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -95,17 +106,31 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{A6428053-78F2-4BF9-85DE-528A92B3FC40}"/>
   </cellStyles>
   <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -126,18 +151,10 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{901EE456-6E81-47AB-B87F-E180DD6DC81C}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -411,14 +428,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="92.140625" customWidth="1"/>
     <col min="2" max="3" width="24.28515625" customWidth="1"/>
-    <col min="4" max="4" width="42.7109375" customWidth="1"/>
+    <col min="4" max="4" width="55.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34" customWidth="1"/>
     <col min="6" max="6" width="38.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -437,33 +454,46 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="str">
+        <f ca="1">"Stock Ageing Report_With Value_As On Dt "&amp;TEXT(TODAY()-1,"dd-MM-yyyy")</f>
+        <v>Stock Ageing Report_With Value_As On Dt 26-06-2026</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
